--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-650.1%</t>
+          <t>-644.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-39.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.1%</t>
+          <t>-286.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-260.0%</t>
+          <t>-253.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-185.1%</t>
+          <t>-181.4%</t>
         </is>
       </c>
     </row>
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.729575403120211</v>
+        <v>3.721599239267058</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.885196943407839</v>
+        <v>-4.824078806108687</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8714911192363142</v>
+        <v>0.8959383741559754</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3603130687397079</v>
+        <v>-0.2991949314405546</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.609738479669373</v>
+        <v>2.646409362048865</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.0%</t>
+          <t>-652.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.2%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.6%</t>
+          <t>-290.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-149.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-253.9%</t>
+          <t>-269.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-190.9%</t>
         </is>
       </c>
     </row>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.929789305927731</v>
+        <v>-4.944033335103716</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8970646408037406</v>
+        <v>0.8913670291333466</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6311834218638501</v>
+        <v>-0.71790491869123</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.490626734370271</v>
+        <v>2.438593836273843</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.07411221185265</v>
+        <v>-5.088356241028634</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8453440088306992</v>
+        <v>0.8396463971603052</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6311834218638501</v>
+        <v>-0.71790491869123</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.496635264767197</v>
+        <v>2.444602366670769</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.926369241617647</v>
+        <v>-4.940613270793632</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9835938447167221</v>
+        <v>0.9778962330463281</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.463376064628967</v>
+        <v>-0.5500975614563468</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.676472326900148</v>
+        <v>2.62443942880372</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.028383924148868</v>
+        <v>-5.042627953324853</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9455815932357146</v>
+        <v>0.9398839815653206</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.463376064628967</v>
+        <v>-0.5500975614563468</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.679265948431629</v>
+        <v>2.627233050335201</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.891774580054776</v>
+        <v>-4.90601860923076</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.00088767926501</v>
+        <v>0.9951900675946159</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3267667205348745</v>
+        <v>-0.4134882173622543</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.761893903279743</v>
+        <v>2.709861005183315</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.034539912877426</v>
+        <v>-5.048783942053411</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.94286202287606</v>
+        <v>0.9371644112056661</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4695320533575249</v>
+        <v>-0.5562535501849047</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.675315180326263</v>
+        <v>2.623282282229835</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.972241914101303</v>
+        <v>-4.986485943277288</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.03411677618333</v>
+        <v>1.028419164512936</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4695320533575249</v>
+        <v>-0.5562535501849047</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.741650734123084</v>
+        <v>2.689617836026656</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.770451716436146</v>
+        <v>-4.78469574561213</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8234137276387912</v>
+        <v>0.8177161159683972</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2715138611883705</v>
+        <v>-0.3582353580157503</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.569042521813975</v>
+        <v>2.517009623717547</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.710561034793552</v>
+        <v>-4.724805063969537</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9176602326180037</v>
+        <v>0.9119626209476097</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.211623179545777</v>
+        <v>-0.2983446763731569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.675267163121706</v>
+        <v>2.623234265025278</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.808301579418527</v>
+        <v>-4.822545608594512</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8931917508840574</v>
+        <v>0.8874941392136635</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2275124576787572</v>
+        <v>-0.3142339545061371</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.680361332357962</v>
+        <v>2.628328434261534</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.984639339541456</v>
+        <v>-4.998883368717441</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8211926276595576</v>
+        <v>0.8154950159891636</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4038502178016866</v>
+        <v>-0.4905717146290665</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.573094657108876</v>
+        <v>2.521061759012448</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.983949967380233</v>
+        <v>-4.998193996556218</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8199599945639753</v>
+        <v>0.8142623828935813</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4038502178016866</v>
+        <v>-0.4905717146290665</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.571586275148804</v>
+        <v>2.519553377052376</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.990520932434825</v>
+        <v>-5.00476496161081</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8171944759775744</v>
+        <v>0.8114968643071805</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4104211828562795</v>
+        <v>-0.4971426796836594</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.567506563551484</v>
+        <v>2.515473665455056</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.982566962140053</v>
+        <v>-4.996810991316038</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8203760640954834</v>
+        <v>0.8146784524250894</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4104211828562795</v>
+        <v>-0.4971426796836594</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.567506563551484</v>
+        <v>2.515473665455056</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.972193585806966</v>
+        <v>-4.986437614982951</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8309071716565226</v>
+        <v>0.8252095599861287</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4000478065231923</v>
+        <v>-0.4867693033505721</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.580112346379142</v>
+        <v>2.528079448282714</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.84450927601267</v>
+        <v>-4.858753305188655</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.886873268948966</v>
+        <v>0.8811756572785721</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2723634967288958</v>
+        <v>-0.3590849935562757</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.661615305630444</v>
+        <v>2.609582407534016</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.905175866415059</v>
+        <v>-4.919419895591044</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8493613052638829</v>
+        <v>0.8436636935934885</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3540618134474295</v>
+        <v>-0.4407833102748093</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.599350988075196</v>
+        <v>2.547318089978768</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.840182006481413</v>
+        <v>-4.854426035657399</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8794565518479696</v>
+        <v>0.8737589401775754</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3272311988432741</v>
+        <v>-0.413952695670654</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.619547059448318</v>
+        <v>2.56751416135189</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.940940642238411</v>
+        <v>-4.955184671414397</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8433140371762484</v>
+        <v>0.837616425505854</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4160567675702795</v>
+        <v>-0.5027782643976594</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.570412657843193</v>
+        <v>2.518379759746765</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.721599239267058</v>
+        <v>3.659350790097659</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.824078806108687</v>
+        <v>-4.910981834328497</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8959383741559754</v>
+        <v>0.8611771628680513</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2991949314405546</v>
+        <v>-0.4585754273117589</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.646409362048865</v>
+        <v>2.550781064526142</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.0%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-35.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-652.7%</t>
+          <t>-653.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.1%</t>
+          <t>-290.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.4%</t>
+          <t>-149.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-269.9%</t>
+          <t>-270.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-190.9%</t>
+          <t>-170.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1983"/>
+  <dimension ref="A1:G1984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.944033335103716</v>
+        <v>-4.956487615893001</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8913670291333466</v>
+        <v>0.8863853168176328</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.71790491869123</v>
+        <v>-0.7260723616414368</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.438593836273843</v>
+        <v>2.433693370503718</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.088356241028634</v>
+        <v>-5.10081052181792</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8396463971603052</v>
+        <v>0.8346646848445909</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.71790491869123</v>
+        <v>-0.7260723616414368</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.444602366670769</v>
+        <v>2.439701900900644</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.940613270793632</v>
+        <v>-4.953067551582917</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9778962330463281</v>
+        <v>0.972914520730614</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5500975614563468</v>
+        <v>-0.5582650044065537</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.62443942880372</v>
+        <v>2.619538963033596</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.042627953324853</v>
+        <v>-5.055082234114138</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9398839815653206</v>
+        <v>0.9349022692496063</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5500975614563468</v>
+        <v>-0.5582650044065537</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.627233050335201</v>
+        <v>2.622332584565077</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.90601860923076</v>
+        <v>-4.918472890020046</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9951900675946159</v>
+        <v>0.9902083552789018</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4134882173622543</v>
+        <v>-0.4216556603124612</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.709861005183315</v>
+        <v>2.704960539413191</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.048783942053411</v>
+        <v>-5.061238222842696</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9371644112056661</v>
+        <v>0.9321826988899522</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5562535501849047</v>
+        <v>-0.5644209931351116</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.623282282229835</v>
+        <v>2.618381816459711</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.986485943277288</v>
+        <v>-4.998940224066573</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.028419164512936</v>
+        <v>1.023437452197222</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5562535501849047</v>
+        <v>-0.5644209931351116</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.689617836026656</v>
+        <v>2.684717370256532</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.78469574561213</v>
+        <v>-4.797150026401416</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8177161159683972</v>
+        <v>0.8127344036526831</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3582353580157503</v>
+        <v>-0.3664028009659572</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.517009623717547</v>
+        <v>2.512109157947422</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.724805063969537</v>
+        <v>-4.737259344758822</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9119626209476097</v>
+        <v>0.9069809086318956</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2983446763731569</v>
+        <v>-0.3065121193233638</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.623234265025278</v>
+        <v>2.618333799255154</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.822545608594512</v>
+        <v>-4.834999889383797</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8874941392136635</v>
+        <v>0.8825124268979496</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3142339545061371</v>
+        <v>-0.3224013974563439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.628328434261534</v>
+        <v>2.623427968491409</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.998883368717441</v>
+        <v>-5.011337649506726</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8154950159891636</v>
+        <v>0.8105133036734493</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4905717146290665</v>
+        <v>-0.4987391575792733</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.521061759012448</v>
+        <v>2.516161293242323</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.998193996556218</v>
+        <v>-5.010648277345503</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8142623828935813</v>
+        <v>0.8092806705778672</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4905717146290665</v>
+        <v>-0.4987391575792733</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.519553377052376</v>
+        <v>2.514652911282252</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.00476496161081</v>
+        <v>-5.017219242400095</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8114968643071805</v>
+        <v>0.8065151519914666</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4971426796836594</v>
+        <v>-0.5053101226338663</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.515473665455056</v>
+        <v>2.510573199684933</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.996810991316038</v>
+        <v>-5.009265272105323</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8146784524250894</v>
+        <v>0.8096967401093753</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4971426796836594</v>
+        <v>-0.5053101226338663</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.515473665455056</v>
+        <v>2.510573199684933</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.986437614982951</v>
+        <v>-4.998891895772236</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8252095599861287</v>
+        <v>0.8202278476704148</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4867693033505721</v>
+        <v>-0.4949367463007791</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.528079448282714</v>
+        <v>2.523178982512589</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.858753305188655</v>
+        <v>-4.87120758597794</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8811756572785721</v>
+        <v>0.876193944962858</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3590849935562757</v>
+        <v>-0.3672524365064826</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.609582407534016</v>
+        <v>2.604681941763892</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.919419895591044</v>
+        <v>-4.93187417638033</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8436636935934885</v>
+        <v>0.8386819812777744</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4407833102748093</v>
+        <v>-0.4489507532250163</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.547318089978768</v>
+        <v>2.542417624208644</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.854426035657399</v>
+        <v>-4.866880316446684</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8737589401775754</v>
+        <v>0.8687772278618613</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.413952695670654</v>
+        <v>-0.4221201386208609</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.56751416135189</v>
+        <v>2.562613695581766</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.955184671414397</v>
+        <v>-4.967638952203682</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.837616425505854</v>
+        <v>0.8326347131901399</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5027782643976594</v>
+        <v>-0.5109457073478663</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.518379759746765</v>
+        <v>2.513479293976641</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,45 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.659350790097659</v>
+        <v>3.826713779163219</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.910981834328497</v>
+        <v>-4.923436115117782</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8611771628680513</v>
+        <v>0.8561954505523373</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4585754273117589</v>
+        <v>-0.4667428702619658</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.550781064526142</v>
+        <v>2.545880598756018</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="2" t="n">
+        <v>45446</v>
+      </c>
+      <c r="B1984" t="n">
+        <v>3.6608029068386</v>
+      </c>
+      <c r="C1984" t="n">
+        <v>2.762344587237751</v>
+      </c>
+      <c r="D1984" t="n">
+        <v>-4.923436115117782</v>
+      </c>
+      <c r="E1984" t="n">
+        <v>0.8561954505523373</v>
+      </c>
+      <c r="F1984" t="n">
+        <v>-0.4667428702619658</v>
+      </c>
+      <c r="G1984" t="n">
+        <v>2.755408384224118</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-50.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-653.9%</t>
+          <t>-652.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.6%</t>
+          <t>-290.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.3%</t>
+          <t>-149.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-270.7%</t>
+          <t>-269.9%</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.956487615893001</v>
+        <v>-4.944033335103716</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8863853168176328</v>
+        <v>0.8913670291333466</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.7260723616414368</v>
+        <v>-0.71790491869123</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.433693370503718</v>
+        <v>2.438593836273843</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.10081052181792</v>
+        <v>-5.088356241028634</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8346646848445909</v>
+        <v>0.8396463971603052</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.7260723616414368</v>
+        <v>-0.71790491869123</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.439701900900644</v>
+        <v>2.444602366670769</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.953067551582917</v>
+        <v>-4.940613270793632</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.972914520730614</v>
+        <v>0.9778962330463281</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5582650044065537</v>
+        <v>-0.5500975614563468</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.619538963033596</v>
+        <v>2.62443942880372</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.055082234114138</v>
+        <v>-5.042627953324853</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9349022692496063</v>
+        <v>0.9398839815653206</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5582650044065537</v>
+        <v>-0.5500975614563468</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.622332584565077</v>
+        <v>2.627233050335201</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.918472890020046</v>
+        <v>-4.90601860923076</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9902083552789018</v>
+        <v>0.9951900675946159</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4216556603124612</v>
+        <v>-0.4134882173622543</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.704960539413191</v>
+        <v>2.709861005183315</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.061238222842696</v>
+        <v>-5.048783942053411</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9321826988899522</v>
+        <v>0.9371644112056661</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5644209931351116</v>
+        <v>-0.5562535501849047</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.618381816459711</v>
+        <v>2.623282282229835</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.998940224066573</v>
+        <v>-4.986485943277288</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.023437452197222</v>
+        <v>1.028419164512936</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5644209931351116</v>
+        <v>-0.5562535501849047</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.684717370256532</v>
+        <v>2.689617836026656</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.797150026401416</v>
+        <v>-4.78469574561213</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8127344036526831</v>
+        <v>0.8177161159683972</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3664028009659572</v>
+        <v>-0.3582353580157503</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.512109157947422</v>
+        <v>2.517009623717547</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.737259344758822</v>
+        <v>-4.724805063969537</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9069809086318956</v>
+        <v>0.9119626209476097</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.3065121193233638</v>
+        <v>-0.2983446763731569</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.618333799255154</v>
+        <v>2.623234265025278</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.834999889383797</v>
+        <v>-4.822545608594512</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8825124268979496</v>
+        <v>0.8874941392136635</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3224013974563439</v>
+        <v>-0.3142339545061371</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.623427968491409</v>
+        <v>2.628328434261534</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.011337649506726</v>
+        <v>-4.998883368717441</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8105133036734493</v>
+        <v>0.8154950159891636</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4987391575792733</v>
+        <v>-0.4905717146290665</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.516161293242323</v>
+        <v>2.521061759012448</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.010648277345503</v>
+        <v>-4.998193996556218</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8092806705778672</v>
+        <v>0.8142623828935813</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4987391575792733</v>
+        <v>-0.4905717146290665</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.514652911282252</v>
+        <v>2.519553377052376</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.017219242400095</v>
+        <v>-5.00476496161081</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8065151519914666</v>
+        <v>0.8114968643071805</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.5053101226338663</v>
+        <v>-0.4971426796836594</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.510573199684933</v>
+        <v>2.515473665455056</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.009265272105323</v>
+        <v>-4.996810991316038</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8096967401093753</v>
+        <v>0.8146784524250894</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.5053101226338663</v>
+        <v>-0.4971426796836594</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.510573199684933</v>
+        <v>2.515473665455056</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.998891895772236</v>
+        <v>-4.986437614982951</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8202278476704148</v>
+        <v>0.8252095599861287</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4949367463007791</v>
+        <v>-0.4867693033505721</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.523178982512589</v>
+        <v>2.528079448282714</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.87120758597794</v>
+        <v>-4.858753305188655</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.876193944962858</v>
+        <v>0.8811756572785721</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3672524365064826</v>
+        <v>-0.3590849935562757</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.604681941763892</v>
+        <v>2.609582407534016</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.93187417638033</v>
+        <v>-4.919419895591044</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8386819812777744</v>
+        <v>0.8436636935934885</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4489507532250163</v>
+        <v>-0.4407833102748093</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.542417624208644</v>
+        <v>2.547318089978768</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.866880316446684</v>
+        <v>-4.854426035657399</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8687772278618613</v>
+        <v>0.8737589401775754</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.4221201386208609</v>
+        <v>-0.413952695670654</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.562613695581766</v>
+        <v>2.56751416135189</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.967638952203682</v>
+        <v>-4.955184671414397</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8326347131901399</v>
+        <v>0.837616425505854</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5109457073478663</v>
+        <v>-0.5027782643976594</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.513479293976641</v>
+        <v>2.518379759746765</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.923436115117782</v>
+        <v>-4.910981834328497</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8561954505523373</v>
+        <v>0.8611771628680513</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4667428702619658</v>
+        <v>-0.4585754273117589</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.545880598756018</v>
+        <v>2.550781064526142</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,13 +47183,13 @@
         <v>2.762344587237751</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.923436115117782</v>
+        <v>-4.910981834328497</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8561954505523373</v>
+        <v>0.8611771628680513</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4667428702619658</v>
+        <v>-0.4585754273117589</v>
       </c>
       <c r="G1984" t="n">
         <v>2.755408384224118</v>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-24.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-652.7%</t>
+          <t>-637.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.1%</t>
+          <t>-284.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.4%</t>
+          <t>-155.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-269.9%</t>
+          <t>-247.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.5%</t>
+          <t>-159.2%</t>
         </is>
       </c>
     </row>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.612550170319184</v>
+        <v>-4.478451236792512</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9040802327145667</v>
+        <v>0.9577198061252354</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4869453346250382</v>
+        <v>-0.3528464010983669</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.457289524380965</v>
+        <v>2.537748884496968</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.695551451344463</v>
+        <v>-4.561452517817791</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7092354403051084</v>
+        <v>0.7628750137157772</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.505516219152212</v>
+        <v>-0.3714172856255407</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.284502713665314</v>
+        <v>2.364962073781317</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.822618457651451</v>
+        <v>-4.688519524124779</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7785582985015187</v>
+        <v>0.8321978719121874</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.505516219152212</v>
+        <v>-0.3714172856255407</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.404652374384519</v>
+        <v>2.485111734500522</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.909217040632554</v>
+        <v>-4.775118107105882</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7584318914114005</v>
+        <v>0.8120714648220693</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.505516219152212</v>
+        <v>-0.3714172856255407</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.419165400486842</v>
+        <v>2.499624760602845</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.870833378074403</v>
+        <v>-4.736734444547731</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7712047977770298</v>
+        <v>0.8248443711876985</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4671325565940608</v>
+        <v>-0.3330336230673895</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.439615039364102</v>
+        <v>2.520074399480105</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.693717048039237</v>
+        <v>-4.559618114512565</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.838780358636398</v>
+        <v>0.8924199320470667</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4671325565940608</v>
+        <v>-0.3330336230673895</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.436344068209404</v>
+        <v>2.516803428325407</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.664014924062943</v>
+        <v>-4.529915990536272</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8513445999888285</v>
+        <v>0.9049841733994972</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4716026818093742</v>
+        <v>-0.3375037482827029</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.434345384842129</v>
+        <v>2.514804744958132</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.484639502824176</v>
+        <v>-4.350540569297504</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9168817437907499</v>
+        <v>0.9705213172014187</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3148259236386555</v>
+        <v>-0.1807269901119842</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.522198415050974</v>
+        <v>2.602657775166977</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.529653716344782</v>
+        <v>-4.39555478281811</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.879683513714097</v>
+        <v>0.9333230871247662</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3451748189532601</v>
+        <v>-0.2110758854265888</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.484796533193801</v>
+        <v>2.565255893309804</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.796658226617217</v>
+        <v>-4.662559293090545</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7785732719440688</v>
+        <v>0.8322128453547379</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5395378569962086</v>
+        <v>-0.4054389234695374</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.373870272706978</v>
+        <v>2.454329632822981</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.89785600805439</v>
+        <v>-4.763757074527717</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7372980812657013</v>
+        <v>0.7909376546763702</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6079466705415277</v>
+        <v>-0.4738477370148566</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.332028906476288</v>
+        <v>2.412488266592291</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.865380421883618</v>
+        <v>-4.731281488356945</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7478882772883269</v>
+        <v>0.8015278506989958</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6079466705415277</v>
+        <v>-0.4738477370148566</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.329628868030605</v>
+        <v>2.410088228146607</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.846342294176321</v>
+        <v>-4.712243360649648</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7520282475794906</v>
+        <v>0.8056678209901598</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6661302818727223</v>
+        <v>-0.532031348346051</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.291243420440133</v>
+        <v>2.371702780556136</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.877468925326939</v>
+        <v>-4.743369991800266</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9171594640579239</v>
+        <v>0.9707990374685929</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6661302818727223</v>
+        <v>-0.532031348346051</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.468825289378814</v>
+        <v>2.549284649494816</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.944033335103716</v>
+        <v>-4.795690372401058</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8913670291333466</v>
+        <v>0.9507042142144098</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.71790491869123</v>
+        <v>-0.4970844883371789</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.438593836273843</v>
+        <v>2.571086094486273</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.088356241028634</v>
+        <v>-4.940013278325977</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8396463971603052</v>
+        <v>0.8989835822413681</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.71790491869123</v>
+        <v>-0.4970844883371789</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.444602366670769</v>
+        <v>2.577094624883199</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.940613270793632</v>
+        <v>-4.792270308090974</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9778962330463281</v>
+        <v>1.037233418127391</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5500975614563468</v>
+        <v>-0.3292771311022957</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.62443942880372</v>
+        <v>2.756931687016151</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.042627953324853</v>
+        <v>-4.894284990622196</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9398839815653206</v>
+        <v>0.9992211666463835</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5500975614563468</v>
+        <v>-0.3292771311022957</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.627233050335201</v>
+        <v>2.759725308547632</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.90601860923076</v>
+        <v>-4.757675646528103</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9951900675946159</v>
+        <v>1.054527252675679</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4134882173622543</v>
+        <v>-0.1926677870082033</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.709861005183315</v>
+        <v>2.842353263395746</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.048783942053411</v>
+        <v>-4.900440979350753</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9371644112056661</v>
+        <v>0.9965015962867292</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5562535501849047</v>
+        <v>-0.3354331198308537</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.623282282229835</v>
+        <v>2.755774540442266</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.986485943277288</v>
+        <v>-4.838142980574631</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.028419164512936</v>
+        <v>1.087756349593999</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5562535501849047</v>
+        <v>-0.3354331198308537</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.689617836026656</v>
+        <v>2.822110094239087</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.78469574561213</v>
+        <v>-4.636352782909473</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8177161159683972</v>
+        <v>0.8770533010494601</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3582353580157503</v>
+        <v>-0.1374149276616993</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.517009623717547</v>
+        <v>2.649501881929977</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.724805063969537</v>
+        <v>-4.57646210126688</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9119626209476097</v>
+        <v>0.9712998060286728</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2983446763731569</v>
+        <v>-0.07752424601910579</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.623234265025278</v>
+        <v>2.755726523237709</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.822545608594512</v>
+        <v>-4.674202645891854</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8874941392136635</v>
+        <v>0.9468313242947266</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.3142339545061371</v>
+        <v>-0.09341352415208598</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.628328434261534</v>
+        <v>2.760820692473964</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.998883368717441</v>
+        <v>-4.850540406014783</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8154950159891636</v>
+        <v>0.8748322010702265</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4905717146290665</v>
+        <v>-0.2697512842750154</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.521061759012448</v>
+        <v>2.653554017224878</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.998193996556218</v>
+        <v>-4.84985103385356</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8142623828935813</v>
+        <v>0.8735995679746444</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4905717146290665</v>
+        <v>-0.2697512842750154</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.519553377052376</v>
+        <v>2.652045635264807</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.00476496161081</v>
+        <v>-4.856421998908153</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8114968643071805</v>
+        <v>0.8708340493882436</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4971426796836594</v>
+        <v>-0.2763222493296083</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.515473665455056</v>
+        <v>2.647965923667487</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.996810991316038</v>
+        <v>-4.848468028613381</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8146784524250894</v>
+        <v>0.8740156375061523</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4971426796836594</v>
+        <v>-0.2763222493296083</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.515473665455056</v>
+        <v>2.647965923667487</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.986437614982951</v>
+        <v>-4.838094652280294</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8252095599861287</v>
+        <v>0.8845467450671918</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4867693033505721</v>
+        <v>-0.265948872996521</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.528079448282714</v>
+        <v>2.660571706495144</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.858753305188655</v>
+        <v>-4.710410342485997</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8811756572785721</v>
+        <v>0.9405128423596352</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3590849935562757</v>
+        <v>-0.1382645632022246</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.609582407534016</v>
+        <v>2.742074665746447</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.919419895591044</v>
+        <v>-4.771076932888386</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8436636935934885</v>
+        <v>0.9030008786745518</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4407833102748093</v>
+        <v>-0.2199628799207582</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.547318089978768</v>
+        <v>2.679810348191199</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.854426035657399</v>
+        <v>-4.70608307295474</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8737589401775754</v>
+        <v>0.9330961252586387</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.413952695670654</v>
+        <v>-0.1931322653166029</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.56751416135189</v>
+        <v>2.700006419564321</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.955184671414397</v>
+        <v>-4.806841708711739</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.837616425505854</v>
+        <v>0.8969536105869174</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.5027782643976594</v>
+        <v>-0.2819578340436083</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.518379759746765</v>
+        <v>2.650872017959196</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.910981834328497</v>
+        <v>-4.762638871625838</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8611771628680513</v>
+        <v>0.9205143479491147</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4585754273117589</v>
+        <v>-0.2377549969577079</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.550781064526142</v>
+        <v>2.683273322738573</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.6608029068386</v>
+        <v>3.848177217337732</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.762344587237751</v>
+        <v>2.875664320618138</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.910981834328497</v>
+        <v>-4.762638871625838</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8611771628680513</v>
+        <v>0.9205143479491147</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4585754273117589</v>
+        <v>-0.2377549969577079</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.755408384224118</v>
+        <v>2.868728117604506</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,55 +811,55 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-51.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-80.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>449.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-637.8%</t>
+          <t>-666.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.2%</t>
+          <t>-295.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-150.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.8%</t>
+          <t>-261.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.2%</t>
+          <t>-186.8%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940722</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.396238184886963</v>
+        <v>-6.550554226397846</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3979517398188324</v>
+        <v>0.336225323214479</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.354186475179349</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.220346092419531</v>
+        <v>-6.374662133930414</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.471907700326454</v>
+        <v>0.4101812837221006</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.354186475179349</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.048899629397067</v>
+        <v>-6.203215670907951</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.553813791589993</v>
+        <v>0.4920873749856396</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.182740012156886</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.823866629728244</v>
+        <v>-5.978182671239128</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6428474690738191</v>
+        <v>0.5811210524694661</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9577070124880632</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.76023088749431</v>
+        <v>-5.914546929005193</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6729965670217104</v>
+        <v>0.611270150417357</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8940712702541287</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.667230846288412</v>
+        <v>-5.821546887799295</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6913908422878654</v>
+        <v>0.629664425683512</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8940712702541287</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.426800349483551</v>
+        <v>-5.581116390994435</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7893061176346867</v>
+        <v>0.7275797010303333</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.6536407734492684</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.354557781312357</v>
+        <v>-5.50887382282324</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8221324587379848</v>
+        <v>0.7604060421336314</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.6536407734492684</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.301559459030969</v>
+        <v>-5.455875500541852</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8440103715678799</v>
+        <v>0.7822839549635265</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5983045144473296</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.192754573551242</v>
+        <v>-5.347070615062125</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8845303969797644</v>
+        <v>0.822803980375411</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5983045144473296</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.972733775514231</v>
+        <v>-5.127049817025115</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9741177532051826</v>
+        <v>0.9123913366008294</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4570846693793493</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.839866086450954</v>
+        <v>-4.994182127961837</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.043159011632317</v>
+        <v>0.9814325950279637</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4570846693793493</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.680350982931584</v>
+        <v>-4.834667024442467</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.108110897480367</v>
+        <v>1.046384480876013</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.2975695658599794</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.535678837831846</v>
+        <v>-4.68999487934273</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.176067858081702</v>
+        <v>1.114341441477348</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.152897420760242</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.595553665189539</v>
+        <v>-4.749869706700422</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.13815541854005</v>
+        <v>1.076429001935697</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.2127722481179341</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.50875416741053</v>
+        <v>-4.663070208921413</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.19527571097422</v>
+        <v>1.133549294369867</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2127722481179341</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.511223873872336</v>
+        <v>-4.665539915383219</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.19436022976291</v>
+        <v>1.132633813158557</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2152419545797403</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.579594060196346</v>
+        <v>-4.733910101707229</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.178019077708008</v>
+        <v>1.116292661103655</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2059662555435253</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.68813224111248</v>
+        <v>-4.842448282623363</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.125040513973446</v>
+        <v>1.063314097369092</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2059662555435253</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.719125400441185</v>
+        <v>-4.873441441952068</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9373528152823503</v>
+        <v>0.8756263986779971</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2059662555435253</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.543651140648716</v>
+        <v>-4.6979671821596</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.012109751191126</v>
+        <v>0.9503833345867723</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2059662555435253</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.654587393289965</v>
+        <v>-4.808903434800849</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9434772788958332</v>
+        <v>0.8817508622914798</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2059662555435253</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.857613970833198</v>
+        <v>-5.011930012344082</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8653980330984454</v>
+        <v>0.8036716164940922</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.4089928330867587</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.699688371897905</v>
+        <v>-4.854004413408789</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.938740659104695</v>
+        <v>0.8770142425003415</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.4089928330867587</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.613444908871528</v>
+        <v>-4.767760950382411</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9681843148891063</v>
+        <v>0.9064578982847531</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.4089928330867587</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.658751728270508</v>
+        <v>-4.813067769781391</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9418373625740399</v>
+        <v>0.8801109459696868</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.4498029960959895</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.75357116580319</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.687784832972809</v>
+        <v>-4.842100874483692</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.930775993726221</v>
+        <v>0.8690495771218678</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.4498029960959895</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.594974351521949</v>
+        <v>-4.749290393032832</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8971728781979307</v>
+        <v>0.8354464615935773</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.3569925146451302</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.639363820851377</v>
+        <v>-4.79367986236226</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8812905663907604</v>
+        <v>0.819564149786407</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4013819839745578</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.526692602615126</v>
+        <v>-4.68100864412601</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9214347621969834</v>
+        <v>0.8597083455926302</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2887107657383076</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.414315601432453</v>
+        <v>-4.568631642943337</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9718768585007198</v>
+        <v>0.9101504418963666</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2887107657383076</v>
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.478451236792512</v>
+        <v>-4.766866211830068</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9577198061252354</v>
+        <v>0.8423538161102133</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3528464010983669</v>
+        <v>-0.4869453346250382</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.537748884496968</v>
+        <v>2.457289524380965</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.561452517817791</v>
+        <v>-4.849867492855346</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7628750137157772</v>
+        <v>0.647509023700755</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3714172856255407</v>
+        <v>-0.505516219152212</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.364962073781317</v>
+        <v>2.284502713665314</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.688519524124779</v>
+        <v>-4.976934499162335</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8321978719121874</v>
+        <v>0.7168318818971655</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3714172856255407</v>
+        <v>-0.505516219152212</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.485111734500522</v>
+        <v>2.404652374384519</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.775118107105882</v>
+        <v>-5.063533082143437</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8120714648220693</v>
+        <v>0.6967054748070471</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3714172856255407</v>
+        <v>-0.505516219152212</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.499624760602845</v>
+        <v>2.419165400486842</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.736734444547731</v>
+        <v>-5.025149419585286</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8248443711876985</v>
+        <v>0.7094783811726764</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3330336230673895</v>
+        <v>-0.4671325565940608</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.520074399480105</v>
+        <v>2.439615039364102</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.559618114512565</v>
+        <v>-4.84803308955012</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8924199320470667</v>
+        <v>0.7770539420320448</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3330336230673895</v>
+        <v>-0.4671325565940608</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.516803428325407</v>
+        <v>2.436344068209404</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.529915990536272</v>
+        <v>-4.818330965573827</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9049841733994972</v>
+        <v>0.7896181833844753</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3375037482827029</v>
+        <v>-0.4716026818093742</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.514804744958132</v>
+        <v>2.434345384842129</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.350540569297504</v>
+        <v>-4.638955544335059</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9705213172014187</v>
+        <v>0.8551553271863968</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1807269901119842</v>
+        <v>-0.3148259236386555</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.602657775166977</v>
+        <v>2.522198415050974</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.39555478281811</v>
+        <v>-4.683969757855666</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9333230871247662</v>
+        <v>0.8179570971097438</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2110758854265888</v>
+        <v>-0.3451748189532601</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.565255893309804</v>
+        <v>2.484796533193801</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.662559293090545</v>
+        <v>-4.950974268128101</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8322128453547379</v>
+        <v>0.7168468553397156</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4054389234695374</v>
+        <v>-0.5395378569962086</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.454329632822981</v>
+        <v>2.373870272706978</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.763757074527717</v>
+        <v>-5.052172049565273</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7909376546763702</v>
+        <v>0.6755716646613479</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4738477370148566</v>
+        <v>-0.6079466705415277</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.412488266592291</v>
+        <v>2.332028906476288</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.731281488356945</v>
+        <v>-5.019696463394501</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8015278506989958</v>
+        <v>0.6861618606839737</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4738477370148566</v>
+        <v>-0.6079466705415277</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.410088228146607</v>
+        <v>2.329628868030605</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.712243360649648</v>
+        <v>-5.000658335687204</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8056678209901598</v>
+        <v>0.6903018309751374</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.532031348346051</v>
+        <v>-0.6661302818727223</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.371702780556136</v>
+        <v>2.291243420440133</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.743369991800266</v>
+        <v>-5.031784966837822</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9707990374685929</v>
+        <v>0.8554330474535705</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.532031348346051</v>
+        <v>-0.6661302818727223</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.549284649494816</v>
+        <v>2.468825289378814</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.795690372401058</v>
+        <v>-5.084105347438614</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9507042142144098</v>
+        <v>0.8353382241993872</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4970844883371789</v>
+        <v>-0.6311834218638501</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.571086094486273</v>
+        <v>2.490626734370271</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.940013278325977</v>
+        <v>-5.228428253363533</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8989835822413681</v>
+        <v>0.7836175922263457</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4970844883371789</v>
+        <v>-0.6311834218638501</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.577094624883199</v>
+        <v>2.496635264767197</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.792270308090974</v>
+        <v>-5.08068528312853</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.037233418127391</v>
+        <v>0.9218674281123689</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3292771311022957</v>
+        <v>-0.463376064628967</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.756931687016151</v>
+        <v>2.676472326900148</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.894284990622196</v>
+        <v>-5.182699965659752</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9992211666463835</v>
+        <v>0.8838551766313612</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3292771311022957</v>
+        <v>-0.463376064628967</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.759725308547632</v>
+        <v>2.679265948431629</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.757675646528103</v>
+        <v>-5.046090621565659</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.054527252675679</v>
+        <v>0.9391612626606567</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1926677870082033</v>
+        <v>-0.3267667205348745</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.842353263395746</v>
+        <v>2.761893903279743</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.900440979350753</v>
+        <v>-5.188855954388309</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9965015962867292</v>
+        <v>0.8811356062717066</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3354331198308537</v>
+        <v>-0.4695320533575249</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.755774540442266</v>
+        <v>2.675315180326263</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.838142980574631</v>
+        <v>-5.126557955612187</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.087756349593999</v>
+        <v>0.9723903595789767</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3354331198308537</v>
+        <v>-0.4695320533575249</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.822110094239087</v>
+        <v>2.741650734123084</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.636352782909473</v>
+        <v>-4.924767757947029</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8770533010494601</v>
+        <v>0.7616873110344378</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1374149276616993</v>
+        <v>-0.2715138611883705</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.649501881929977</v>
+        <v>2.569042521813975</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.57646210126688</v>
+        <v>-4.864877076304436</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9712998060286728</v>
+        <v>0.8559338160136503</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.07752424601910579</v>
+        <v>-0.211623179545777</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.755726523237709</v>
+        <v>2.675267163121706</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.674202645891854</v>
+        <v>-4.96261762092941</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9468313242947266</v>
+        <v>0.8314653342797043</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09341352415208598</v>
+        <v>-0.2275124576787572</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.760820692473964</v>
+        <v>2.680361332357962</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.850540406014783</v>
+        <v>-5.138955381052339</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8748322010702265</v>
+        <v>0.7594662110552042</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2697512842750154</v>
+        <v>-0.4038502178016866</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.653554017224878</v>
+        <v>2.573094657108876</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.84985103385356</v>
+        <v>-5.138266008891116</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8735995679746444</v>
+        <v>0.7582335779596221</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2697512842750154</v>
+        <v>-0.4038502178016866</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.652045635264807</v>
+        <v>2.571586275148804</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.856421998908153</v>
+        <v>-5.144836973945709</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8708340493882436</v>
+        <v>0.755468059373221</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2763222493296083</v>
+        <v>-0.4104211828562795</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.647965923667487</v>
+        <v>2.567506563551484</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.848468028613381</v>
+        <v>-5.136883003650937</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8740156375061523</v>
+        <v>0.7586496474911302</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2763222493296083</v>
+        <v>-0.4104211828562795</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.647965923667487</v>
+        <v>2.567506563551484</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.838094652280294</v>
+        <v>-5.12650962731785</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8845467450671918</v>
+        <v>0.7691807550521692</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.265948872996521</v>
+        <v>-0.4000478065231923</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.660571706495144</v>
+        <v>2.580112346379142</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.710410342485997</v>
+        <v>-4.998825317523553</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9405128423596352</v>
+        <v>0.8251468523446128</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1382645632022246</v>
+        <v>-0.2723634967288958</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.742074665746447</v>
+        <v>2.661615305630444</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.771076932888386</v>
+        <v>-5.059491907925942</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9030008786745518</v>
+        <v>0.7876348886595297</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.2199628799207582</v>
+        <v>-0.3540618134474295</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.679810348191199</v>
+        <v>2.599350988075196</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.70608307295474</v>
+        <v>-4.994498047992296</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9330961252586387</v>
+        <v>0.8177301352436164</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1931322653166029</v>
+        <v>-0.3272311988432741</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.700006419564321</v>
+        <v>2.619547059448318</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.806841708711739</v>
+        <v>-5.095256683749295</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8969536105869174</v>
+        <v>0.7815876205718952</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2819578340436083</v>
+        <v>-0.4160567675702795</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.650872017959196</v>
+        <v>2.570412657843193</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163219</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.762638871625838</v>
+        <v>-5.051053846663394</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9205143479491147</v>
+        <v>0.8051483579340926</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2377549969577079</v>
+        <v>-0.3718539304843791</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.683273322738573</v>
+        <v>2.60281396262257</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.848177217337732</v>
+        <v>3.43645848104732</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.875664320618138</v>
+        <v>2.599559033849252</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.762638871625838</v>
+        <v>-5.051053846663394</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9205143479491147</v>
+        <v>0.8051483579340926</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.2377549969577079</v>
+        <v>-0.3718539304843791</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.868728117604506</v>
+        <v>2.59262283083562</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,55 +811,55 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-29.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-683.5%</t>
+          <t>-690.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.3%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.7%</t>
+          <t>-651.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.8%</t>
+          <t>-276.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>366.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.7%</t>
+          <t>-289.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-303.4%</t>
+          <t>-310.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-150.6%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-261.2%</t>
+          <t>-267.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-182.5%</t>
+          <t>-186.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-186.8%</t>
+          <t>-189.9%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.074651412279923</v>
+        <v>-2.142010902993139</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.286703278216148</v>
+        <v>2.259759481930862</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6699985588688046</v>
+        <v>0.602639068155589</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.518919402763148</v>
+        <v>3.478503708335218</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.413809789868445</v>
+        <v>-2.481169280581661</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.144124226487188</v>
+        <v>2.117180430201902</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3308401812802825</v>
+        <v>0.2634806905670669</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.308508675516483</v>
+        <v>3.268092981088554</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.62230057132013</v>
+        <v>-2.689660062033346</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.081066203645283</v>
+        <v>2.054122407359996</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.122349399828598</v>
+        <v>0.05498990911538248</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.203752496384241</v>
+        <v>3.163336801956312</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.869501756085351</v>
+        <v>-2.936861246798567</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.990284480147762</v>
+        <v>1.963340683862477</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1425027533274105</v>
+        <v>0.07514326261419491</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.223943258892097</v>
+        <v>3.183527564464168</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.361886784109448</v>
+        <v>-3.429246274822664</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.794436860981856</v>
+        <v>1.76749306469657</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3498822746966863</v>
+        <v>-0.4172417654099018</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.929618634121371</v>
+        <v>2.889202939693442</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.747067175039521</v>
+        <v>-3.814426665752736</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.63890724342269</v>
+        <v>1.611963447137404</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3498822746966863</v>
+        <v>-0.4172417654099018</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.928161172934234</v>
+        <v>2.887745478506305</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.090749948266184</v>
+        <v>-4.158109438979399</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.503203257586641</v>
+        <v>1.476259461301355</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4577883267239045</v>
+        <v>-0.52514781743712</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.86518666517252</v>
+        <v>2.82477097074459</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.297261725153205</v>
+        <v>-4.36462121586642</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.416704605488091</v>
+        <v>1.389760809202804</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.664300103610926</v>
+        <v>-0.7316595943241415</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.737385657696565</v>
+        <v>2.696969963268635</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.553102810931898</v>
+        <v>-4.620462301645113</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.316141097876873</v>
+        <v>1.289197301591587</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.664300103610926</v>
+        <v>-0.7316595943241415</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.739158584396824</v>
+        <v>2.698742889968895</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.984908604081685</v>
+        <v>-5.052268094794901</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.129751668084363</v>
+        <v>1.102807871799076</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8007176000521929</v>
+        <v>-0.8680770907654085</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.643640973999468</v>
+        <v>2.603225279571539</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.219602598214237</v>
+        <v>-5.286962088927453</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.024158845433432</v>
+        <v>0.9972150491481462</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7943813328229378</v>
+        <v>-0.8617408235361533</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.635727509339112</v>
+        <v>2.595311814911183</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.55526524544469</v>
+        <v>-5.622624736157905</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8884743781972166</v>
+        <v>0.8615305819119303</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7943813328229378</v>
+        <v>-0.8617408235361533</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.634308100995077</v>
+        <v>2.593892406567148</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.918891490345003</v>
+        <v>-5.986250981058219</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7495114404713328</v>
+        <v>0.7225676441860465</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8926029696900636</v>
+        <v>-0.9599624604032791</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.581862679109043</v>
+        <v>2.541446984681114</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.28401887298375</v>
+        <v>-6.351378363696965</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6027150024216654</v>
+        <v>0.5757712061363791</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.188913753989076</v>
+        <v>-1.256273244702292</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.403330723535467</v>
+        <v>2.362915029107538</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.692607650164428</v>
+        <v>-6.759967140877643</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4380410355641531</v>
+        <v>0.4110972392788668</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.597502531169755</v>
+        <v>-1.66486202188297</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.156939001241819</v>
+        <v>2.11652330681389</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.96918375048026</v>
+        <v>-7.036543241193476</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.322596027909281</v>
+        <v>0.2956522316239947</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.597502531169755</v>
+        <v>-1.66486202188297</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.15212443371328</v>
+        <v>2.11170873928535</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.385575624767258</v>
+        <v>-7.452935115480473</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1540333288033593</v>
+        <v>0.127089532518073</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.597502531169755</v>
+        <v>-1.66486202188297</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.150118484322157</v>
+        <v>2.109702789894228</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.702187567307906</v>
+        <v>-7.769547058021121</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03764724245577877</v>
+        <v>0.0107034461704929</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.597502531169755</v>
+        <v>-1.66486202188297</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.160377174990836</v>
+        <v>2.119961480562907</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.048062389292715</v>
+        <v>-8.115421880005931</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1046031211924494</v>
+        <v>-0.1315469174777357</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.597502531169755</v>
+        <v>-1.66486202188297</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.156476740136531</v>
+        <v>2.116061045708602</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.211642267477099</v>
+        <v>-8.279001758190315</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1716301524112023</v>
+        <v>-0.1985739486964886</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.597502531169755</v>
+        <v>-1.66486202188297</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.154881660191532</v>
+        <v>2.114465965763603</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.508303609287298</v>
+        <v>-8.575663100000513</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2865157132060734</v>
+        <v>-0.3134595094913597</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.666245666903633</v>
+        <v>-1.733605157616849</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.117414754680413</v>
+        <v>2.076999060252484</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.713334790061614</v>
+        <v>-8.78069428077483</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3725544900502031</v>
+        <v>-0.3994982863354894</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.666245666903633</v>
+        <v>-1.733605157616849</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.11338845014601</v>
+        <v>2.072972755718081</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.096336178804245</v>
+        <v>-9.163695669517461</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5258571468688396</v>
+        <v>-0.5528009431541259</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.666245666903633</v>
+        <v>-1.733605157616849</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.113286348824426</v>
+        <v>2.072870654396497</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.27820596978928</v>
+        <v>-9.345565460502495</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5960335472914235</v>
+        <v>-0.6229773435767094</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.848115457888668</v>
+        <v>-1.915474948601884</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.006735990204835</v>
+        <v>1.966320295776906</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.637736292293281</v>
+        <v>-9.705095783006497</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7344953729949739</v>
+        <v>-0.7614391692802602</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.848115457888668</v>
+        <v>-1.915474948601884</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.012086293502885</v>
+        <v>1.971670599074956</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.688085355747504</v>
+        <v>-9.755444846460719</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.746718978419485</v>
+        <v>-0.7736627747047713</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.89846452134289</v>
+        <v>-1.965824012056106</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.98979287538753</v>
+        <v>1.9493771809596</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.785704633168899</v>
+        <v>-9.853064123882115</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7827249387662749</v>
+        <v>-0.8096687350515608</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.996083798764287</v>
+        <v>-2.063443289477502</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.934263059556461</v>
+        <v>1.893847365128531</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.933230721174542</v>
+        <v>-10.00059021188776</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8388418176469599</v>
+        <v>-0.8657856139322457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.14360988676993</v>
+        <v>-2.210969377483146</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.848640963074647</v>
+        <v>1.808225268646717</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.13748889650441</v>
+        <v>-10.20484838721762</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9150318906602628</v>
+        <v>-0.9419756869455487</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.271248831383919</v>
+        <v>-2.338608322097135</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.777570793424896</v>
+        <v>1.737155098996966</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.27929867071119</v>
+        <v>-10.34665816142441</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9672732458585416</v>
+        <v>-0.9942170421438283</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.442527629029495</v>
+        <v>-2.50988711974271</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.679286069321986</v>
+        <v>1.638870374894057</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.20582883904375</v>
+        <v>-10.27318832975696</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9225136116981414</v>
+        <v>-0.9494574079834273</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.369057797362046</v>
+        <v>-2.436417288075262</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.738739669815877</v>
+        <v>1.698323975387947</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.38095325643029</v>
+        <v>-10.4483127471435</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9780081579052418</v>
+        <v>-1.004951954190528</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.54418221474859</v>
+        <v>-2.611541705461806</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.648220240131467</v>
+        <v>1.607804545703538</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.61540535044478</v>
+        <v>-10.68276484115799</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.079008160412634</v>
+        <v>-1.10595195669792</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.54418221474859</v>
+        <v>-2.611541705461806</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.641001075229871</v>
+        <v>1.600585380801942</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.90320919498202</v>
+        <v>-10.97056868569523</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.200801889001505</v>
+        <v>-1.227745685286792</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.831986059285828</v>
+        <v>-2.899345549999044</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.461646577733552</v>
+        <v>1.421230883305623</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.95599535058234</v>
+        <v>-11.02335484129556</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.220800561403079</v>
+        <v>-1.247744357688366</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.927661545868225</v>
+        <v>-2.995021036581441</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.40535707562267</v>
+        <v>1.364941381194741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.08203214395063</v>
+        <v>-11.14939163466385</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.26852155012128</v>
+        <v>-1.295465346406567</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.902409923058483</v>
+        <v>-2.969769413771699</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.42320177793763</v>
+        <v>1.382786083509701</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.03001662998182</v>
+        <v>-11.09737612069503</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.243725008847354</v>
+        <v>-1.270668805132641</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.902409923058483</v>
+        <v>-2.969769413771699</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.427192113624031</v>
+        <v>1.386776419196102</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.17168847170594</v>
+        <v>-11.23904796241916</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.301868972435744</v>
+        <v>-1.328812768721031</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.902409923058483</v>
+        <v>-2.969769413771699</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.425716886725289</v>
+        <v>1.38530119229736</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.12209762728111</v>
+        <v>-11.18945711799432</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.266979224500938</v>
+        <v>-1.293923020786224</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.852819078633649</v>
+        <v>-2.920178569346865</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.470524803545062</v>
+        <v>1.430109109117133</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.92294552004401</v>
+        <v>-10.99030501075722</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.200369515252782</v>
+        <v>-1.227313311538068</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.687496552683836</v>
+        <v>-2.754856043397051</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.556667185468267</v>
+        <v>1.516251491040338</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.69710036732459</v>
+        <v>-10.76445985803781</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.100452381128809</v>
+        <v>-1.127396177414095</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.645569877096672</v>
+        <v>-2.712929367809888</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.591402263856774</v>
+        <v>1.550986569428844</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.572521710987</v>
+        <v>-10.63988120170022</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.049481774037713</v>
+        <v>-1.076425570322999</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.645569877096672</v>
+        <v>-2.712929367809888</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.592541408412833</v>
+        <v>1.552125713984903</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.62541699903129</v>
+        <v>-10.6927764897445</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.068006115093319</v>
+        <v>-1.094949911378606</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.640614531008226</v>
+        <v>-2.707974021721442</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.598148390228008</v>
+        <v>1.557732695800079</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34150826810254</v>
+        <v>-10.40886775881576</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9487089184831836</v>
+        <v>-0.9756527147684695</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.640614531008226</v>
+        <v>-2.707974021721442</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.603882094466645</v>
+        <v>1.563466400038715</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27014187549289</v>
+        <v>-10.33750136620611</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9298996238331902</v>
+        <v>-0.9568434201184761</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.569248138398578</v>
+        <v>-2.636607629111794</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.636964667638568</v>
+        <v>1.596548973210639</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.00630500828882</v>
+        <v>-10.07366449900204</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8342483582644697</v>
+        <v>-0.8611921545497556</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.569248138398578</v>
+        <v>-2.636607629111794</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.62708118632566</v>
+        <v>1.586665491897731</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.739063207420426</v>
+        <v>-9.806422698133641</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.729186198416484</v>
+        <v>-0.7561299947017703</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.569248138398578</v>
+        <v>-2.636607629111794</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.625246625826287</v>
+        <v>1.584830931398357</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.641156168743935</v>
+        <v>-9.70851565945715</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6903236979193488</v>
+        <v>-0.7172674942046351</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.501262388538022</v>
+        <v>-2.568621879251237</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.66573776076916</v>
+        <v>1.62532206634123</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.617202627767977</v>
+        <v>-9.684562118481193</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6800737753834718</v>
+        <v>-0.7070175716687581</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.477308847562064</v>
+        <v>-2.54466833827528</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.680778391500228</v>
+        <v>1.640362697072298</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.35314268944518</v>
+        <v>-9.420502180158396</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5877101162161056</v>
+        <v>-0.6146539125013915</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.213248909239268</v>
+        <v>-2.280608399952484</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.825954038332153</v>
+        <v>1.785538343904224</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.646063065940343</v>
+        <v>-8.713422556653558</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3076653004744712</v>
+        <v>-0.3346090967597575</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.213248909239268</v>
+        <v>-2.280608399952484</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.823167004671852</v>
+        <v>1.782751310243923</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.605878767574152</v>
+        <v>-8.673238258287368</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2912479572401536</v>
+        <v>-0.3181917535254399</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.173064610873078</v>
+        <v>-2.240424101586293</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.847621207579408</v>
+        <v>1.807205513151479</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.525808972036348</v>
+        <v>-8.593168462749563</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2598532178042752</v>
+        <v>-0.2867970140895615</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.092994815335274</v>
+        <v>-2.160354306048489</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.895029906122848</v>
+        <v>1.854614211694918</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.292327749806748</v>
+        <v>-8.359687240519964</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1585363000745827</v>
+        <v>-0.1854800963598691</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.859513593105675</v>
+        <v>-1.926873083818891</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.043043068298459</v>
+        <v>2.00262737387053</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.142661358799234</v>
+        <v>-8.21002084951245</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1015619539845365</v>
+        <v>-0.1285057502698228</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.766610101863139</v>
+        <v>-1.833969592576355</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.095892952731021</v>
+        <v>2.055477258303092</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.010385885168347</v>
+        <v>-8.077745375881562</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05328427778515454</v>
+        <v>-0.08022807407044086</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.634334628232252</v>
+        <v>-1.701694118945468</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.170625723656581</v>
+        <v>2.130210029228651</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.819786210495194</v>
+        <v>-7.88714570120841</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.0257706527717434</v>
+        <v>-0.001173143513542918</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.4437349535591</v>
+        <v>-1.511094444272315</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.287800589148109</v>
+        <v>2.24738489472018</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.570786411811613</v>
+        <v>-7.638145902524829</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1382769134688346</v>
+        <v>0.1113331171835483</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.4437349535591</v>
+        <v>-1.511094444272315</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.300706930371768</v>
+        <v>2.260291235943838</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.676376401584718</v>
+        <v>-7.743735892297933</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03193501203962601</v>
+        <v>-0.05887880832491232</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.549324943332204</v>
+        <v>-1.616684434045419</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.109377006908686</v>
+        <v>2.068961312480757</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.695111303703315</v>
+        <v>-7.76247079441653</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.009115368990021633</v>
+        <v>-0.01782842729526468</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.549324943332204</v>
+        <v>-1.616684434045419</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157921348785773</v>
+        <v>2.117505654357843</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.547171262295715</v>
+        <v>-7.614530753008931</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05158753713510622</v>
+        <v>-0.07853133342039254</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529004027423646</v>
+        <v>-1.596363518136862</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.05023497564274</v>
+        <v>2.00981928121481</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.530013112164421</v>
+        <v>-7.597372602877637</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0534382633360666</v>
+        <v>-0.08038205962135292</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.511845877292352</v>
+        <v>-1.579205368005568</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.051815879468038</v>
+        <v>2.011400185040109</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.486464705393731</v>
+        <v>-7.553824196106946</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.04297951272288358</v>
+        <v>-0.0699233090081699</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.511845877292352</v>
+        <v>-1.579205368005568</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.044855267372945</v>
+        <v>2.004439572945016</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.244316311939873</v>
+        <v>-7.311675802653088</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.06834219903980276</v>
+        <v>0.04139840275451645</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.511845877292352</v>
+        <v>-1.579205368005568</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.059317621754088</v>
+        <v>2.018901927326159</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.136057174817351</v>
+        <v>-7.203416665530566</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1061779743480065</v>
+        <v>0.07923417806272015</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.511845877292352</v>
+        <v>-1.579205368005568</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.053849742213283</v>
+        <v>2.013434047785354</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.01276604000022</v>
+        <v>-7.080125530713436</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1529925222854356</v>
+        <v>0.1260487260001493</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.388554742475221</v>
+        <v>-1.455914233188437</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.125322517114138</v>
+        <v>2.084906822686209</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.991616841096777</v>
+        <v>-7.058976331809992</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1691531800841379</v>
+        <v>0.1422093837988516</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.367405543571778</v>
+        <v>-1.434765034284994</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.14571301469353</v>
+        <v>2.1052973202656</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.747851399113332</v>
+        <v>-6.815210889826548</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2624400652245664</v>
+        <v>0.2354962689392801</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.367405543571778</v>
+        <v>-1.434765034284994</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.14149372304058</v>
+        <v>2.101078028612651</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.646088578836038</v>
+        <v>-6.713448069549253</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3052695072555003</v>
+        <v>0.278325710970214</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.354186475179349</v>
+        <v>-1.421545965892565</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.151549477996054</v>
+        <v>2.111133783568124</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.550554226397846</v>
+        <v>-6.463597675600179</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.336225323214479</v>
+        <v>0.371007943533546</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.354186475179349</v>
+        <v>-1.421545965892565</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.144291552979756</v>
+        <v>2.103875858551826</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.374662133930414</v>
+        <v>-6.287705583132746</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4101812837221006</v>
+        <v>0.4449639040411677</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.354186475179349</v>
+        <v>-1.421545965892565</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.147890676500404</v>
+        <v>2.107474982072475</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.203215670907951</v>
+        <v>-6.116259120110283</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4920873749856396</v>
+        <v>0.5268699953047067</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.182740012156886</v>
+        <v>-1.250099502870102</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.264086060368436</v>
+        <v>2.223670365940507</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.978182671239128</v>
+        <v>-5.89122612044146</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5811210524694661</v>
+        <v>0.6159036727885332</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9577070124880632</v>
+        <v>-1.025066503201279</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.398126337786027</v>
+        <v>2.357710643358097</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.914546929005193</v>
+        <v>-5.827590378207526</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.611270150417357</v>
+        <v>0.6460527707364241</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8940712702541287</v>
+        <v>-0.9614307609673441</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.441002584180705</v>
+        <v>2.400586889752775</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.821546887799295</v>
+        <v>-5.734590337001627</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.629664425683512</v>
+        <v>0.6644470460025791</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8940712702541287</v>
+        <v>-0.9614307609673441</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.4221968429645</v>
+        <v>2.381781148536571</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.581116390994435</v>
+        <v>-5.494159840196767</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7275797010303333</v>
+        <v>0.7623623213494004</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6536407734492684</v>
+        <v>-0.7210002641624839</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.568198217672294</v>
+        <v>2.527782523244364</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.50887382282324</v>
+        <v>-5.421917272025572</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7604060421336314</v>
+        <v>0.7951886624526985</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6536407734492684</v>
+        <v>-0.7210002641624839</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.572127531507114</v>
+        <v>2.531711837079185</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.455875500541852</v>
+        <v>-5.368918949744184</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7822839549635265</v>
+        <v>0.8170665752825936</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5983045144473296</v>
+        <v>-0.665664005160545</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.606007870825617</v>
+        <v>2.565592176397688</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.347070615062125</v>
+        <v>-5.260114064264457</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.822803980375411</v>
+        <v>0.8575866006944781</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5983045144473296</v>
+        <v>-0.665664005160545</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.603005942045611</v>
+        <v>2.562590247617682</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.127049817025115</v>
+        <v>-5.040093266227447</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9123913366008294</v>
+        <v>0.9471739569198965</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4570846693793493</v>
+        <v>-0.5244441600925648</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.689316886097013</v>
+        <v>2.648901191669084</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.994182127961837</v>
+        <v>-4.907225577164169</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9814325950279637</v>
+        <v>1.016215215347031</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4570846693793493</v>
+        <v>-0.5244441600925648</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.705211068898836</v>
+        <v>2.664795374470907</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.834667024442467</v>
+        <v>-4.747710473644799</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.046384480876013</v>
+        <v>1.081167101195081</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2975695658599794</v>
+        <v>-0.3649290565731949</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.80206597545076</v>
+        <v>2.761650281022831</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.68999487934273</v>
+        <v>-4.603038328545062</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.114341441477348</v>
+        <v>1.149124061796415</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.152897420760242</v>
+        <v>-0.2202569114734574</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.898957365072043</v>
+        <v>2.858541670644113</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.749869706700422</v>
+        <v>-4.662913155902754</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.076429001935697</v>
+        <v>1.111211622254764</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2127722481179341</v>
+        <v>-0.2801317388311496</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.849069960058853</v>
+        <v>2.808654265630924</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.663070208921413</v>
+        <v>-4.576113658123745</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.133549294369867</v>
+        <v>1.168331914688934</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2127722481179341</v>
+        <v>-0.2801317388311496</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.871470453381419</v>
+        <v>2.83105475895349</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.665539915383219</v>
+        <v>-4.578583364585551</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.132633813158557</v>
+        <v>1.167416433477624</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2152419545797403</v>
+        <v>-0.2826014452929557</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.870061030877748</v>
+        <v>2.829645336449818</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.733910101707229</v>
+        <v>-4.646953550909561</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.116292661103655</v>
+        <v>1.151075281422722</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2059662555435253</v>
+        <v>-0.2733257462567408</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.886633372774178</v>
+        <v>2.846217678346249</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.842448282623363</v>
+        <v>-4.755491731825695</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.063314097369092</v>
+        <v>1.09809671768816</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2059662555435253</v>
+        <v>-0.2733257462567408</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.87707008140607</v>
+        <v>2.83665438697814</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.873441441952068</v>
+        <v>-4.786484891154401</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8756263986779971</v>
+        <v>0.9104090189970642</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2059662555435253</v>
+        <v>-0.2733257462567408</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.701779646446457</v>
+        <v>2.661363952018527</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.6979671821596</v>
+        <v>-4.611010631361932</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9503833345867723</v>
+        <v>0.9851659549058394</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2059662555435253</v>
+        <v>-0.2733257462567408</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.706346878438245</v>
+        <v>2.665931184010315</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.808903434800849</v>
+        <v>-4.721946884003181</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8817508622914798</v>
+        <v>0.9165334826105469</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2059662555435253</v>
+        <v>-0.2733257462567408</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.682088907199452</v>
+        <v>2.641673212771522</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.011930012344082</v>
+        <v>-4.924973461546414</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8036716164940922</v>
+        <v>0.8384542368131591</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4089928330867587</v>
+        <v>-0.4763523237999742</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.563404345893417</v>
+        <v>2.522988651465488</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.854004413408789</v>
+        <v>-4.767047862611121</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8770142425003415</v>
+        <v>0.9117968628194086</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4089928330867587</v>
+        <v>-0.4763523237999742</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.57357673232555</v>
+        <v>2.53316103789762</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.767760950382411</v>
+        <v>-4.680804399584743</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9064578982847531</v>
+        <v>0.9412405186038202</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4089928330867587</v>
+        <v>-0.4763523237999742</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.56852300289941</v>
+        <v>2.528107308471481</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.813067769781391</v>
+        <v>-4.726111218983723</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8801109459696868</v>
+        <v>0.9148935662887538</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4498029960959895</v>
+        <v>-0.517162486809205</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.535812680538397</v>
+        <v>2.495396986110467</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.842100874483692</v>
+        <v>-4.755144323686024</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8690495771218678</v>
+        <v>0.9038321974409349</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4498029960959895</v>
+        <v>-0.517162486809205</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.536364553571498</v>
+        <v>2.495948859143569</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.749290393032832</v>
+        <v>-4.662333842235165</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8354464615935773</v>
+        <v>0.8702290819126444</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3569925146451302</v>
+        <v>-0.4243520053583456</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.52132353433338</v>
+        <v>2.48090783990545</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.79367986236226</v>
+        <v>-4.706723311564592</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.819564149786407</v>
+        <v>0.8543467701054741</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4013819839745578</v>
+        <v>-0.4687414746877733</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.496563328660324</v>
+        <v>2.456147634232395</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.68100864412601</v>
+        <v>-4.594052093328342</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8597083455926302</v>
+        <v>0.8944909659116973</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2887107657383076</v>
+        <v>-0.3560702564515231</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.559241768113797</v>
+        <v>2.518826073685868</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.568631642943337</v>
+        <v>-4.481675092145669</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9101504418963666</v>
+        <v>0.9449330622154337</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2887107657383076</v>
+        <v>-0.3560702564515231</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.564733063944464</v>
+        <v>2.524317369516535</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.766866211830068</v>
+        <v>-4.6799096610324</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8423538161102133</v>
+        <v>0.8771364364292804</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4869453346250382</v>
+        <v>-0.5543048253382536</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.457289524380965</v>
+        <v>2.416873829953036</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.849867492855346</v>
+        <v>-4.762910942057679</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.647509023700755</v>
+        <v>0.6822916440198221</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.505516219152212</v>
+        <v>-0.5728757098654274</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.284502713665314</v>
+        <v>2.244087019237385</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.976934499162335</v>
+        <v>-4.889977948364667</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7168318818971655</v>
+        <v>0.7516145022162326</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.505516219152212</v>
+        <v>-0.5728757098654274</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.404652374384519</v>
+        <v>2.364236679956591</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.063533082143437</v>
+        <v>-4.97657653134577</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6967054748070471</v>
+        <v>0.7314880951261142</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.505516219152212</v>
+        <v>-0.5728757098654274</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.419165400486842</v>
+        <v>2.378749706058914</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.025149419585286</v>
+        <v>-4.938192868787619</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7094783811726764</v>
+        <v>0.7442610014917435</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4671325565940608</v>
+        <v>-0.5344920473072762</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.439615039364102</v>
+        <v>2.399199344936173</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.84803308955012</v>
+        <v>-4.761076538752453</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7770539420320448</v>
+        <v>0.8118365623511119</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4671325565940608</v>
+        <v>-0.5344920473072762</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.436344068209404</v>
+        <v>2.395928373781475</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.818330965573827</v>
+        <v>-4.731374414776159</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7896181833844753</v>
+        <v>0.8244008037035424</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4716026818093742</v>
+        <v>-0.5389621725225895</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.434345384842129</v>
+        <v>2.3939296904142</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.638955544335059</v>
+        <v>-4.551998993537391</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8551553271863968</v>
+        <v>0.8899379475054638</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3148259236386555</v>
+        <v>-0.3821854143518708</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.522198415050974</v>
+        <v>2.481782720623045</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.683969757855666</v>
+        <v>-4.597013207057998</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8179570971097438</v>
+        <v>0.8527397174288109</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3451748189532601</v>
+        <v>-0.4125343096664754</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.484796533193801</v>
+        <v>2.444380838765873</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.950974268128101</v>
+        <v>-4.864017717330433</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7168468553397156</v>
+        <v>0.7516294756587827</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5395378569962086</v>
+        <v>-0.6068973477094239</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.373870272706978</v>
+        <v>2.333454578279049</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.052172049565273</v>
+        <v>-4.965215498767606</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6755716646613479</v>
+        <v>0.710354284980415</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6079466705415277</v>
+        <v>-0.6753061612547431</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.332028906476288</v>
+        <v>2.291613212048359</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.019696463394501</v>
+        <v>-4.932739912596833</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6861618606839737</v>
+        <v>0.7209444810030405</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6079466705415277</v>
+        <v>-0.6753061612547431</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.329628868030605</v>
+        <v>2.289213173602676</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.000658335687204</v>
+        <v>-4.913701784889536</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6903018309751374</v>
+        <v>0.7250844512942045</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6661302818727223</v>
+        <v>-0.7334897725859376</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.291243420440133</v>
+        <v>2.250827726012204</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.031784966837822</v>
+        <v>-4.944828416040155</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8554330474535705</v>
+        <v>0.8902156677726376</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6661302818727223</v>
+        <v>-0.7334897725859376</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.468825289378814</v>
+        <v>2.428409594950884</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.084105347438614</v>
+        <v>-4.997148796640946</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8353382241993872</v>
+        <v>0.8701208445184545</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6311834218638501</v>
+        <v>-0.6985429125770655</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.490626734370271</v>
+        <v>2.450211039942341</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.228428253363533</v>
+        <v>-5.141471702565865</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.7836175922263457</v>
+        <v>0.8184002125454128</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6311834218638501</v>
+        <v>-0.6985429125770655</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.496635264767197</v>
+        <v>2.456219570339267</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.08068528312853</v>
+        <v>-4.993728732330863</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9218674281123689</v>
+        <v>0.9566500484314358</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.463376064628967</v>
+        <v>-0.5307355553421823</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.676472326900148</v>
+        <v>2.636056632472219</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.182699965659752</v>
+        <v>-5.095743414862084</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8838551766313612</v>
+        <v>0.9186377969504282</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.463376064628967</v>
+        <v>-0.5307355553421823</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.679265948431629</v>
+        <v>2.6388502540037</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.046090621565659</v>
+        <v>-4.959134070767991</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9391612626606567</v>
+        <v>0.9739438829797238</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3267667205348745</v>
+        <v>-0.3941262112480898</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.761893903279743</v>
+        <v>2.721478208851814</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.188855954388309</v>
+        <v>-5.101899403590641</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8811356062717066</v>
+        <v>0.9159182265907737</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4695320533575249</v>
+        <v>-0.5368915440707402</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.675315180326263</v>
+        <v>2.634899485898334</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.126557955612187</v>
+        <v>-5.039601404814519</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9723903595789767</v>
+        <v>1.007172979898044</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4695320533575249</v>
+        <v>-0.5368915440707402</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.741650734123084</v>
+        <v>2.701235039695155</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.924767757947029</v>
+        <v>-4.837811207149361</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7616873110344378</v>
+        <v>0.7964699313535049</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2715138611883705</v>
+        <v>-0.3388733519015859</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.569042521813975</v>
+        <v>2.528626827386045</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.864877076304436</v>
+        <v>-4.777920525506768</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8559338160136503</v>
+        <v>0.8907164363327174</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.211623179545777</v>
+        <v>-0.2789826702589924</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.675267163121706</v>
+        <v>2.634851468693777</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.96261762092941</v>
+        <v>-4.875661070131742</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8314653342797043</v>
+        <v>0.8662479545987714</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2275124576787572</v>
+        <v>-0.2948719483919726</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.680361332357962</v>
+        <v>2.639945637930032</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.138955381052339</v>
+        <v>-5.051998830254671</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7594662110552042</v>
+        <v>0.7942488313742713</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4038502178016866</v>
+        <v>-0.471209708514902</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.573094657108876</v>
+        <v>2.532678962680946</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.138266008891116</v>
+        <v>-5.051309458093448</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7582335779596221</v>
+        <v>0.7930161982786892</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4038502178016866</v>
+        <v>-0.471209708514902</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.571586275148804</v>
+        <v>2.531170580720875</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.144836973945709</v>
+        <v>-5.057880423148041</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.755468059373221</v>
+        <v>0.7902506796922881</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4104211828562795</v>
+        <v>-0.4777806735694949</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.567506563551484</v>
+        <v>2.527090869123555</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.136883003650937</v>
+        <v>-5.049926452853269</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7586496474911302</v>
+        <v>0.7934322678101973</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4104211828562795</v>
+        <v>-0.4777806735694949</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.567506563551484</v>
+        <v>2.527090869123555</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.12650962731785</v>
+        <v>-5.039553076520182</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7691807550521692</v>
+        <v>0.8039633753712363</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4000478065231923</v>
+        <v>-0.4674072972364076</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.580112346379142</v>
+        <v>2.539696651951212</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.998825317523553</v>
+        <v>-4.911868766725886</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8251468523446128</v>
+        <v>0.8599294726636799</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2723634967288958</v>
+        <v>-0.3397229874421112</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.661615305630444</v>
+        <v>2.621199611202515</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.059491907925942</v>
+        <v>-4.972535357128274</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7876348886595297</v>
+        <v>0.8224175089785966</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3540618134474295</v>
+        <v>-0.4214213041606448</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.599350988075196</v>
+        <v>2.558935293647267</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.994498047992296</v>
+        <v>-4.907541497194629</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8177301352436164</v>
+        <v>0.8525127555626835</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3272311988432741</v>
+        <v>-0.3945906895564895</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.619547059448318</v>
+        <v>2.579131365020389</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.095256683749295</v>
+        <v>-5.008300132951627</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7815876205718952</v>
+        <v>0.8163702408909621</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4160567675702795</v>
+        <v>-0.4834162582834949</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.570412657843193</v>
+        <v>2.529996963415264</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.051053846663394</v>
+        <v>-4.964097295865726</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8051483579340926</v>
+        <v>0.8399309782531594</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.3718539304843791</v>
+        <v>-0.4392134211975944</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.60281396262257</v>
+        <v>2.562398268194641</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.43645848104732</v>
+        <v>3.75413982781873</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.599559033849252</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.051053846663394</v>
+        <v>-4.901587522923072</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8051483579340926</v>
+        <v>0.8633448878994687</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3718539304843791</v>
+        <v>-0.4392134211975944</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.59262283083562</v>
+        <v>2.560808268663888</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240603.xlsx
+++ b/tame_output/ON/bt/strategyON_20240603.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -763,12 +763,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,27 +819,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-27.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>128.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-52.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>448.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-651.7%</t>
+          <t>-655.2%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-36.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>366.0%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-289.9%</t>
+          <t>-289.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-158.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-267.9%</t>
+          <t>-284.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-189.9%</t>
+          <t>-198.6%</t>
         </is>
       </c>
     </row>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.99030501075722</v>
+        <v>-11.19400417667904</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.227313311538068</v>
+        <v>-1.308792977906794</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.754856043397051</v>
+        <v>-2.979959152910891</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.516251491040338</v>
+        <v>1.381189625332034</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.76445985803781</v>
+        <v>-10.96815902395963</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.127396177414095</v>
+        <v>-1.208875843782821</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.712929367809888</v>
+        <v>-2.938032477323727</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.550986569428844</v>
+        <v>1.415924703720541</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.63988120170022</v>
+        <v>-10.84358036762203</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.076425570322999</v>
+        <v>-1.157905236691725</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.712929367809888</v>
+        <v>-2.938032477323727</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.552125713984903</v>
+        <v>1.4170638482766</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.6927764897445</v>
+        <v>-10.89647565566632</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.094949911378606</v>
+        <v>-1.176429577747332</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.707974021721442</v>
+        <v>-2.933077131235281</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.557732695800079</v>
+        <v>1.422670830091775</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.40886775881576</v>
+        <v>-10.61256692473757</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9756527147684695</v>
+        <v>-1.057132381137196</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.707974021721442</v>
+        <v>-2.933077131235281</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.563466400038715</v>
+        <v>1.428404534330412</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.33750136620611</v>
+        <v>-10.54120053212792</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9568434201184761</v>
+        <v>-1.038323086487202</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.636607629111794</v>
+        <v>-2.861710738625633</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.596548973210639</v>
+        <v>1.461487107502335</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.07366449900204</v>
+        <v>-10.27736366492385</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8611921545497556</v>
+        <v>-0.9426718209184819</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.636607629111794</v>
+        <v>-2.861710738625633</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.586665491897731</v>
+        <v>1.451603626189428</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.806422698133641</v>
+        <v>-10.01012186405546</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7561299947017703</v>
+        <v>-0.8376096610704962</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.636607629111794</v>
+        <v>-2.861710738625633</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.584830931398357</v>
+        <v>1.449769065690054</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.70851565945715</v>
+        <v>-9.912214825378966</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7172674942046351</v>
+        <v>-0.7987471605733609</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.568621879251237</v>
+        <v>-2.793724988765076</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.62532206634123</v>
+        <v>1.490260200632927</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.684562118481193</v>
+        <v>-9.888261284403008</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7070175716687581</v>
+        <v>-0.7884972380374844</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.54466833827528</v>
+        <v>-2.769771447789119</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.640362697072298</v>
+        <v>1.505300831363995</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.420502180158396</v>
+        <v>-9.624201346080211</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6146539125013915</v>
+        <v>-0.6961335788701177</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.280608399952484</v>
+        <v>-2.505711509466323</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.785538343904224</v>
+        <v>1.650476478195921</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.713422556653558</v>
+        <v>-8.917121722575374</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3346090967597575</v>
+        <v>-0.4160887631284838</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.280608399952484</v>
+        <v>-2.505711509466323</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.782751310243923</v>
+        <v>1.64768944453562</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.673238258287368</v>
+        <v>-8.876937424209183</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3181917535254399</v>
+        <v>-0.3996714198941662</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.240424101586293</v>
+        <v>-2.465527211100132</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.807205513151479</v>
+        <v>1.672143647443176</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.593168462749563</v>
+        <v>-8.796867628671379</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2867970140895615</v>
+        <v>-0.3682766804582873</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.160354306048489</v>
+        <v>-2.385457415562328</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.854614211694918</v>
+        <v>1.719552345986615</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.359687240519964</v>
+        <v>-8.563386406441779</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1854800963598691</v>
+        <v>-0.2669597627285953</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.926873083818891</v>
+        <v>-2.151976193332729</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.00262737387053</v>
+        <v>1.867565508162227</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.21002084951245</v>
+        <v>-8.413720015434265</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1285057502698228</v>
+        <v>-0.2099854166385486</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.833969592576355</v>
+        <v>-2.059072702090193</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.055477258303092</v>
+        <v>1.920415392594789</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.077745375881562</v>
+        <v>-8.281444541803378</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08022807407044086</v>
+        <v>-0.1617077404391667</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.701694118945468</v>
+        <v>-1.926797228459306</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.130210029228651</v>
+        <v>1.995148163520348</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.88714570120841</v>
+        <v>-8.090844867130224</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.001173143513542918</v>
+        <v>-0.08265280988226875</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.511094444272315</v>
+        <v>-1.736197553786154</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.24738489472018</v>
+        <v>2.112323029011876</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.638145902524829</v>
+        <v>-7.841845068446643</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1113331171835483</v>
+        <v>0.02985345081482249</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.511094444272315</v>
+        <v>-1.736197553786154</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.260291235943838</v>
+        <v>2.125229370235536</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.743735892297933</v>
+        <v>-7.947435058219748</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05887880832491232</v>
+        <v>-0.1403584746936382</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.616684434045419</v>
+        <v>-1.841787543559258</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.068961312480757</v>
+        <v>1.933899446772454</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.76247079441653</v>
+        <v>-7.966169960338345</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01782842729526468</v>
+        <v>-0.09930809366399052</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.616684434045419</v>
+        <v>-1.841787543559258</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.117505654357843</v>
+        <v>1.98244378864954</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.614530753008931</v>
+        <v>-7.818229918930745</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07853133342039254</v>
+        <v>-0.1600109997891184</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.596363518136862</v>
+        <v>-1.8214666276507</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.00981928121481</v>
+        <v>1.874757415506507</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.597372602877637</v>
+        <v>-7.801071768799451</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08038205962135292</v>
+        <v>-0.1618617259900788</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.579205368005568</v>
+        <v>-1.804308477519406</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.011400185040109</v>
+        <v>1.876338319331806</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.553824196106946</v>
+        <v>-7.757523362028761</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0699233090081699</v>
+        <v>-0.1514029753768957</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.579205368005568</v>
+        <v>-1.804308477519406</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.004439572945016</v>
+        <v>1.869377707236713</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.311675802653088</v>
+        <v>-7.515374968574903</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04139840275451645</v>
+        <v>-0.04008126361420938</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.579205368005568</v>
+        <v>-1.804308477519406</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.018901927326159</v>
+        <v>1.883840061617856</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.203416665530566</v>
+        <v>-7.407115831452381</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07923417806272015</v>
+        <v>-0.002245488306005683</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.579205368005568</v>
+        <v>-1.804308477519406</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.013434047785354</v>
+        <v>1.878372182077051</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.080125530713436</v>
+        <v>-7.28382469663525</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1260487260001493</v>
+        <v>0.04456905963142344</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.455914233188437</v>
+        <v>-1.681017342702276</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.084906822686209</v>
+        <v>1.949844956977905</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.058976331809992</v>
+        <v>-7.262675497731807</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1422093837988516</v>
+        <v>0.06072971743012623</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.434765034284994</v>
+        <v>-1.659868143798832</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.1052973202656</v>
+        <v>1.970235454557297</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.815210889826548</v>
+        <v>-7.018910055748362</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2354962689392801</v>
+        <v>0.1540166025705543</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.434765034284994</v>
+        <v>-1.659868143798832</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.101078028612651</v>
+        <v>1.966016162904348</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.713448069549253</v>
+        <v>-6.917147235471067</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.278325710970214</v>
+        <v>0.1968460446014886</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.421545965892565</v>
+        <v>-1.646649075406404</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.111133783568124</v>
+        <v>1.976071917859821</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.463597675600179</v>
+        <v>-6.667296841521993</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.371007943533546</v>
+        <v>0.2895282771648202</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.421545965892565</v>
+        <v>-1.646649075406404</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.103875858551826</v>
+        <v>1.968813992843523</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.287705583132746</v>
+        <v>-6.49140474905456</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4449639040411677</v>
+        <v>0.3634842376724423</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.421545965892565</v>
+        <v>-1.646649075406404</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.107474982072475</v>
+        <v>1.972413116364172</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.116259120110283</v>
+        <v>-6.319958286032096</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5268699953047067</v>
+        <v>0.4453903289359813</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.250099502870102</v>
+        <v>-1.47520261238394</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.223670365940507</v>
+        <v>2.088608500232203</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.89122612044146</v>
+        <v>-6.094925286363273</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6159036727885332</v>
+        <v>0.5344240064198074</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.025066503201279</v>
+        <v>-1.250169612715117</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.357710643358097</v>
+        <v>2.222648777649794</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.827590378207526</v>
+        <v>-6.031289544129339</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6460527707364241</v>
+        <v>0.5645731043676987</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9614307609673441</v>
+        <v>-1.186533870481183</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.400586889752775</v>
+        <v>2.265525024044472</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.734590337001627</v>
+        <v>-5.938289502923441</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6644470460025791</v>
+        <v>0.5829673796338537</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9614307609673441</v>
+        <v>-1.186533870481183</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.381781148536571</v>
+        <v>2.246719282828268</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.494159840196767</v>
+        <v>-5.697859006118581</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7623623213494004</v>
+        <v>0.680882654980675</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7210002641624839</v>
+        <v>-0.9461033736763227</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.527782523244364</v>
+        <v>2.392720657536061</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.421917272025572</v>
+        <v>-5.625616437947386</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7951886624526985</v>
+        <v>0.7137089960839731</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7210002641624839</v>
+        <v>-0.9461033736763227</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.531711837079185</v>
+        <v>2.396649971370882</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.368918949744184</v>
+        <v>-5.572618115665998</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8170665752825936</v>
+        <v>0.7355869089138682</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.665664005160545</v>
+        <v>-0.8907671146743839</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.565592176397688</v>
+        <v>2.430530310689385</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.260114064264457</v>
+        <v>-5.463813230186271</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8575866006944781</v>
+        <v>0.7761069343257527</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.665664005160545</v>
+        <v>-0.8907671146743839</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.562590247617682</v>
+        <v>2.427528381909378</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.040093266227447</v>
+        <v>-5.24379243214926</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9471739569198965</v>
+        <v>0.8656942905511711</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5244441600925648</v>
+        <v>-0.7495472696064036</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.648901191669084</v>
+        <v>2.513839325960781</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.907225577164169</v>
+        <v>-5.110924743085983</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.016215215347031</v>
+        <v>0.9347355489783054</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5244441600925648</v>
+        <v>-0.7495472696064036</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.664795374470907</v>
+        <v>2.529733508762604</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.747710473644799</v>
+        <v>-4.951409639566613</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.081167101195081</v>
+        <v>0.9996874348263551</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3649290565731949</v>
+        <v>-0.5900321660870337</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.761650281022831</v>
+        <v>2.626588415314528</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.603038328545062</v>
+        <v>-4.806737494466875</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.149124061796415</v>
+        <v>1.06764439542769</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2202569114734574</v>
+        <v>-0.4453600209872963</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.858541670644113</v>
+        <v>2.72347980493581</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.662913155902754</v>
+        <v>-4.866612321824568</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.111211622254764</v>
+        <v>1.029731955886039</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2801317388311496</v>
+        <v>-0.5052348483449884</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.808654265630924</v>
+        <v>2.673592399922621</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.576113658123745</v>
+        <v>-4.779812824045559</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.168331914688934</v>
+        <v>1.086852248320209</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2801317388311496</v>
+        <v>-0.5052348483449884</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.83105475895349</v>
+        <v>2.695992893245187</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.578583364585551</v>
+        <v>-4.782282530507365</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.167416433477624</v>
+        <v>1.085936767108898</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2826014452929557</v>
+        <v>-0.5077045548067947</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.829645336449818</v>
+        <v>2.694583470741515</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.132252912958836</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.646953550909561</v>
+        <v>-4.850652716831375</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.151075281422722</v>
+        <v>1.191635401912539</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2733257462567408</v>
+        <v>-0.4984288557705797</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.846217678346249</v>
+        <v>2.833195599496488</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.122689621590727</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.755491731825695</v>
+        <v>-4.959190897747509</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.09809671768816</v>
+        <v>1.138656838177976</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2733257462567408</v>
+        <v>-0.4984288557705797</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.83665438697814</v>
+        <v>2.82363230812838</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>2.947399186631114</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.786484891154401</v>
+        <v>-4.990184057076214</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9104090189970642</v>
+        <v>0.9509691394868811</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2733257462567408</v>
+        <v>-0.4984288557705797</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.661363952018527</v>
+        <v>2.648341873168766</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>2.951966418622902</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.611010631361932</v>
+        <v>-4.814709797283745</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9851659549058394</v>
+        <v>1.025726075395656</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2733257462567408</v>
+        <v>-0.4984288557705797</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.665931184010315</v>
+        <v>2.652909105160554</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>2.927708447384109</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.721946884003181</v>
+        <v>-4.925646049924994</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9165334826105469</v>
+        <v>0.9570936031003638</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2733257462567408</v>
+        <v>-0.4984288557705797</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.641673212771522</v>
+        <v>2.628651133921761</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>2.930839832604014</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.924973461546414</v>
+        <v>-5.128672627468227</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8384542368131591</v>
+        <v>0.8790143573029763</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4763523237999742</v>
+        <v>-0.7014554333138131</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.522988651465488</v>
+        <v>2.509966572615727</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>2.941012219036147</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.767047862611121</v>
+        <v>-4.970747028532934</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9117968628194086</v>
+        <v>0.9523569833092256</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4763523237999742</v>
+        <v>-0.7014554333138131</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.53316103789762</v>
+        <v>2.520138959047859</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>2.935958489610007</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.680804399584743</v>
+        <v>-4.884503565506557</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9412405186038202</v>
+        <v>0.9818006390936371</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4763523237999742</v>
+        <v>-0.7014554333138131</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.528107308471481</v>
+        <v>2.515085229621719</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>2.927734265054533</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.726111218983723</v>
+        <v>-4.929810384905537</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9148935662887538</v>
+        <v>0.9554536867785708</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.517162486809205</v>
+        <v>-0.7422655963230439</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.495396986110467</v>
+        <v>2.482374907260707</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.75357116580319</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>2.928286138087634</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.755144323686024</v>
+        <v>-4.958843489607838</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9038321974409349</v>
+        <v>0.9443923179307518</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.517162486809205</v>
+        <v>-0.7422655963230439</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.495948859143569</v>
+        <v>2.482926780293808</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>2.857558829979</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.662333842235165</v>
+        <v>-4.866033008156978</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8702290819126444</v>
+        <v>0.9107892024024613</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4243520053583456</v>
+        <v>-0.6494551148721845</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.48090783990545</v>
+        <v>2.467885761055689</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>2.859432305903601</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.706723311564592</v>
+        <v>-4.910422477486406</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8543467701054741</v>
+        <v>0.894906890595291</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4687414746877733</v>
+        <v>-0.6938445842016122</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.456147634232395</v>
+        <v>2.443125555382633</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>2.854508014415324</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.594052093328342</v>
+        <v>-4.797751259250155</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8944909659116973</v>
+        <v>0.9350510864015142</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3560702564515231</v>
+        <v>-0.5811733659653621</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.518826073685868</v>
+        <v>2.505803994836107</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>2.859999310245991</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.481675092145669</v>
+        <v>-4.685374258067482</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9449330622154337</v>
+        <v>0.9854931827052507</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3560702564515231</v>
+        <v>-0.5811733659653621</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.524317369516535</v>
+        <v>2.511295290666774</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>2.87149651201453</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.6799096610324</v>
+        <v>-4.883608826954213</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8771364364292804</v>
+        <v>0.9176965569190974</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5543048253382536</v>
+        <v>-0.7794079348520927</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.416873829953036</v>
+        <v>2.403851751103275</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.709852232015183</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.762910942057679</v>
+        <v>-4.966610107979492</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6822916440198221</v>
+        <v>0.7228517645096391</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5728757098654274</v>
+        <v>-0.7979788193792664</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.244087019237385</v>
+        <v>2.231064940387624</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>2.830001892734389</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.889977948364667</v>
+        <v>-5.09367711428648</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7516145022162326</v>
+        <v>0.7921746227060495</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5728757098654274</v>
+        <v>-0.7979788193792664</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.364236679956591</v>
+        <v>2.351214601106829</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>2.844514918836712</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.97657653134577</v>
+        <v>-5.180275697267583</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7314880951261142</v>
+        <v>0.7720482156159312</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5728757098654274</v>
+        <v>-0.7979788193792664</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.378749706058914</v>
+        <v>2.365727627209152</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>2.841934360179081</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.938192868787619</v>
+        <v>-5.141892034709432</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7442610014917435</v>
+        <v>0.7848211219815604</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5344920473072762</v>
+        <v>-0.7595951568211152</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.399199344936173</v>
+        <v>2.386177266086412</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>2.838663389024383</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.761076538752453</v>
+        <v>-4.964775704674266</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8118365623511119</v>
+        <v>0.8523966828409293</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5344920473072762</v>
+        <v>-0.7595951568211152</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.395928373781475</v>
+        <v>2.382906294931714</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>2.839346780786296</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.731374414776159</v>
+        <v>-4.935073580697972</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8244008037035424</v>
+        <v>0.8649609241933598</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5389621725225895</v>
+        <v>-0.7640652820364285</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.3939296904142</v>
+        <v>2.380907611564439</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>2.83313375609271</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.551998993537391</v>
+        <v>-4.755698159459205</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8899379475054638</v>
+        <v>0.9304980679952812</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3821854143518708</v>
+        <v>-0.6072885238657099</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.481782720623045</v>
+        <v>2.468760641773285</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>2.8139412114243</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.597013207057998</v>
+        <v>-4.800712372979811</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8527397174288109</v>
+        <v>0.8932998379186283</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4125343096664754</v>
+        <v>-0.6376374191803145</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.444380838765873</v>
+        <v>2.431358759916112</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>2.819632773763246</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.864017717330433</v>
+        <v>-5.067716883252246</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7516294756587827</v>
+        <v>0.7921895961485999</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6068973477094239</v>
+        <v>-0.832000457223263</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.333454578279049</v>
+        <v>2.320432499429288</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>2.818836695659747</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.965215498767606</v>
+        <v>-5.168914664689419</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.710354284980415</v>
+        <v>0.7509144054702324</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.6753061612547431</v>
+        <v>-0.9004092707685821</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.291613212048359</v>
+        <v>2.278591133198598</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>2.816436657214064</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.932739912596833</v>
+        <v>-5.136439078518647</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7209444810030405</v>
+        <v>0.7615046014928581</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.6753061612547431</v>
+        <v>-0.9004092707685821</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.289213173602676</v>
+        <v>2.276191094752915</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>2.812961376422309</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.913701784889536</v>
+        <v>-5.11740095081135</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7250844512942045</v>
+        <v>0.7656445717840219</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.7334897725859376</v>
+        <v>-0.9585928820997767</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.250827726012204</v>
+        <v>2.237805647162443</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>2.990543245360989</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.944828416040155</v>
+        <v>-5.148527581961968</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8902156677726376</v>
+        <v>0.930775788262455</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.7334897725859376</v>
+        <v>-0.9585928820997767</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.428409594950884</v>
+        <v>2.415387516101124</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>2.991376574347123</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.997148796640946</v>
+        <v>-5.20084796256276</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8701208445184545</v>
+        <v>0.9106809650082717</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6985429125770655</v>
+        <v>-0.9236460220909045</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.450211039942341</v>
+        <v>2.437188961092581</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>2.997385104744049</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.141471702565865</v>
+        <v>-5.345170868487679</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8184002125454128</v>
+        <v>0.8589603330352302</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6985429125770655</v>
+        <v>-0.9236460220909045</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.456219570339267</v>
+        <v>2.443197491489506</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.076537752536071</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.993728732330863</v>
+        <v>-5.197427898252676</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9566500484314358</v>
+        <v>0.9972101689212534</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.5307355553421823</v>
+        <v>-0.7558386648560214</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.636056632472219</v>
+        <v>2.623034553622459</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.079331374067552</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.095743414862084</v>
+        <v>-5.299442580783897</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9186377969504282</v>
+        <v>0.9591979174402456</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.5307355553421823</v>
+        <v>-0.7558386648560214</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.6388502540037</v>
+        <v>2.62582817515394</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.07999372245921</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.959134070767991</v>
+        <v>-5.162833236689805</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9739438829797238</v>
+        <v>1.014504003469541</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3941262112480898</v>
+        <v>-0.6192293207619289</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.721478208851814</v>
+        <v>2.708456130002053</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.07907419919932</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.101899403590641</v>
+        <v>-5.305598569512455</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9159182265907737</v>
+        <v>0.9564783470805911</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.5368915440707402</v>
+        <v>-0.7619946535845793</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.634899485898334</v>
+        <v>2.621877407048573</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.145409752996141</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.039601404814519</v>
+        <v>-5.243300570736332</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.007172979898044</v>
+        <v>1.047733100387861</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.5368915440707402</v>
+        <v>-0.7619946535845793</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.701235039695155</v>
+        <v>2.688212960845394</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.853990625385539</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.837811207149361</v>
+        <v>-5.041510373071175</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7964699313535049</v>
+        <v>0.8370300518433225</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.3388733519015859</v>
+        <v>-0.5639764614154249</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.528626827386045</v>
+        <v>2.515604748536285</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.924280857707715</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.777920525506768</v>
+        <v>-4.981619691428581</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8907164363327174</v>
+        <v>0.9312765568225347</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2789826702589924</v>
+        <v>-0.5040857797728314</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.634851468693777</v>
+        <v>2.621829389844016</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.938908593823758</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.875661070131742</v>
+        <v>-5.079360236053556</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8662479545987714</v>
+        <v>0.9068080750885885</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2948719483919726</v>
+        <v>-0.5199750579058117</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.639945637930032</v>
+        <v>2.626923559080272</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.93744457464843</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.051998830254671</v>
+        <v>-5.255697996176485</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7942488313742713</v>
+        <v>0.8348089518640887</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.471209708514902</v>
+        <v>-0.6963128180287411</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.532678962680946</v>
+        <v>2.519656883831185</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.935936192688358</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.051309458093448</v>
+        <v>-5.255008624015262</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7930161982786892</v>
+        <v>0.8335763187685066</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.471209708514902</v>
+        <v>-0.6963128180287411</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.531170580720875</v>
+        <v>2.518148501871114</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.935799060123795</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.057880423148041</v>
+        <v>-5.261579589069854</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7902506796922881</v>
+        <v>0.8308108001821055</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.4777806735694949</v>
+        <v>-0.702883783083334</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.527090869123555</v>
+        <v>2.514068790273795</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.935799060123795</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.049926452853269</v>
+        <v>-5.253625618775082</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7934322678101973</v>
+        <v>0.8339923883000147</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.4777806735694949</v>
+        <v>-0.702883783083334</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.527090869123555</v>
+        <v>2.514068790273795</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.942180817151599</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.039553076520182</v>
+        <v>-5.243252242441995</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.8039633753712363</v>
+        <v>0.8445234958610537</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.4674072972364076</v>
+        <v>-0.6925104067502467</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.539696651951212</v>
+        <v>2.526674573101451</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.947073190526324</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.911868766725886</v>
+        <v>-5.115567932647699</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8599294726636799</v>
+        <v>0.9004895931534973</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.3397229874421112</v>
+        <v>-0.5648260969559502</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.621199611202515</v>
+        <v>2.608177532352754</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.933827863002196</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.972535357128274</v>
+        <v>-5.176234523050088</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8224175089785966</v>
+        <v>0.8629776294684142</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.4214213041606448</v>
+        <v>-0.6465244136744839</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.558935293647267</v>
+        <v>2.545913214797507</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.937925565612825</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.907541497194629</v>
+        <v>-5.111240663116442</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8525127555626835</v>
+        <v>0.8930728760525009</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3945906895564895</v>
+        <v>-0.6196937990703285</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.579131365020389</v>
+        <v>2.566109286170628</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.942086505243903</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.008300132951627</v>
+        <v>-5.21199929887344</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8163702408909621</v>
+        <v>0.8569303613807797</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.4834162582834949</v>
+        <v>-0.7085193677973339</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.529996963415264</v>
+        <v>2.516974884565503</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.94796610777174</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.964097295865726</v>
+        <v>-5.11043178937771</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8399309782531594</v>
+        <v>0.903436967706909</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.4392134211975944</v>
+        <v>-0.606951858301604</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.562398268194641</v>
+        <v>2.583794992790778</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.75413982781873</v>
+        <v>3.434766096412587</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.838733918908555</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.901587522923072</v>
+        <v>-4.93587824938447</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8633448878994687</v>
+        <v>0.8640261948410197</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.4392134211975944</v>
+        <v>-0.606951858301604</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.560808268663888</v>
+        <v>2.474562803927593</v>
       </c>
     </row>
   </sheetData>
